--- a/public/Template Jasa.xlsx
+++ b/public/Template Jasa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\Ecommerce-Banjarsari\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9530DA11-6FC9-448D-ACB6-D59E9E95D778}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03195AEE-679C-4D5B-9D3B-EE29F76F08ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,7 +117,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -127,6 +127,14 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -163,7 +171,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
